--- a/Research Setup/Matriks_Sintesis_Literatur.xlsx
+++ b/Research Setup/Matriks_Sintesis_Literatur.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Habbi Widagdo\Documents\Tugas Akhir\Proposal TA\Research Setup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01AA6B06-23CE-4496-BDB9-F9E84AB197C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C42B867-4ED9-4240-A86C-267C3B4AF53E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -123,18 +123,12 @@
     <t>Ivan Tomek (1976)</t>
   </si>
   <si>
-    <t>Keterbatasan Condensed Nearest Neighbor (CNN) yang menahan sampel internal tidak perlu alih-alih sampel batas (boundary samples).</t>
-  </si>
-  <si>
     <t>Synthetic 2D Two-Class Benchmark Dataset (Domain Pengenalan Pola Teoretis).</t>
   </si>
   <si>
     <t>Ordered CNN (Method 1 &amp; Method 2) untuk mengidentifikasi dan menyeleksi pasangan sampel terdekat di batas kelas (Tomek Links).</t>
   </si>
   <si>
-    <t>Ukuran subset tereduksi (E ⊂ D) dan Akurasi Klasifikasi 1-NN.</t>
-  </si>
-  <si>
     <t>Modifikasi Tomek berhasil memperkecil ukuran dataset sekaligus mempertahankan titik-titik batas keputusan secara presisi dengan menghapus sampel bising di sekitar garis batas.</t>
   </si>
   <si>
@@ -571,13 +565,19 @@
   </si>
   <si>
     <t>Geospatial Soil Phosphorus Dataset (Tanzania &amp; Canada); Domain Sensing Nutrisi Tanah / Soil Probing; Tidak tersedia publik.</t>
+  </si>
+  <si>
+    <t>Keterbatasan Condensed Nearest Neighbor (CNN) yang menahan sampel internal yang tidak perlu sebagai pengganti sampel batas (boundary samples).</t>
+  </si>
+  <si>
+    <t>Ukuran subset tereduksi dan Akurasi Klasifikasi 1-NN.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -633,6 +633,21 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -717,7 +732,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -749,18 +764,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -789,6 +792,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1111,13 +1123,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>2</v>
@@ -1143,31 +1155,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C2" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E2" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="F2" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="G2" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="H2" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="I2" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="J2" s="10" t="s">
         <v>32</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="J2" s="10" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="113.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1175,63 +1187,63 @@
         <v>2</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C3" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="E3" s="10" t="s">
+      <c r="H3" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="F3" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" s="10" t="s">
+      <c r="I3" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="J3" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="I3" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="J3" s="10" t="s">
-        <v>40</v>
-      </c>
     </row>
     <row r="4" spans="1:10" ht="130.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11">
+      <c r="A4" s="21">
         <v>3</v>
       </c>
-      <c r="B4" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="C4" s="12" t="s">
+      <c r="B4" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="D4" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="E4" s="14" t="s">
+      <c r="G4" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="H4" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="I4" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="J4" s="23" t="s">
         <v>59</v>
-      </c>
-      <c r="I4" s="14" t="s">
-        <v>60</v>
-      </c>
-      <c r="J4" s="14" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="96" customHeight="1" x14ac:dyDescent="0.25">
@@ -1239,13 +1251,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>10</v>
@@ -1267,34 +1279,34 @@
       </c>
     </row>
     <row r="6" spans="1:10" ht="113.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="15">
+      <c r="A6" s="11">
         <v>5</v>
       </c>
-      <c r="B6" s="16" t="s">
-        <v>169</v>
-      </c>
-      <c r="C6" s="16" t="s">
+      <c r="B6" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="C6" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="E6" s="18" t="s">
+      <c r="D6" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="E6" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="18" t="s">
+      <c r="G6" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="18" t="s">
+      <c r="H6" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="I6" s="18" t="s">
+      <c r="I6" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J6" s="18" t="s">
+      <c r="J6" s="14" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1303,22 +1315,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C7" s="8" t="s">
         <v>23</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>24</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H7" s="10" t="s">
         <v>25</v>
@@ -1331,35 +1343,35 @@
       </c>
     </row>
     <row r="8" spans="1:10" ht="128.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="15">
+      <c r="A8" s="11">
         <v>7</v>
       </c>
-      <c r="B8" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="C8" s="16" t="s">
+      <c r="B8" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="F8" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="D8" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="E8" s="18" t="s">
+      <c r="G8" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="F8" s="18" t="s">
+      <c r="H8" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="G8" s="18" t="s">
+      <c r="I8" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="H8" s="18" t="s">
+      <c r="J8" s="14" t="s">
         <v>66</v>
-      </c>
-      <c r="I8" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="J8" s="18" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="112.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1367,63 +1379,63 @@
         <v>8</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C9" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="E9" s="10" t="s">
+      <c r="G9" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="H9" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="I9" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="H9" s="10" t="s">
+      <c r="J9" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="I9" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="J9" s="10" t="s">
-        <v>54</v>
-      </c>
     </row>
     <row r="10" spans="1:10" ht="114" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="15">
+      <c r="A10" s="11">
         <v>9</v>
       </c>
-      <c r="B10" s="16" t="s">
-        <v>164</v>
-      </c>
-      <c r="C10" s="16" t="s">
+      <c r="B10" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="E10" s="18" t="s">
+      <c r="G10" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="18" t="s">
+      <c r="H10" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="G10" s="18" t="s">
+      <c r="I10" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="H10" s="18" t="s">
+      <c r="J10" s="14" t="s">
         <v>45</v>
-      </c>
-      <c r="I10" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="J10" s="18" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="115.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1431,31 +1443,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="C11" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="F11" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="D11" s="20" t="s">
-        <v>153</v>
-      </c>
-      <c r="E11" s="21" t="s">
+      <c r="G11" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="F11" s="21" t="s">
+      <c r="H11" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="G11" s="21" t="s">
+      <c r="I11" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="H11" s="21" t="s">
+      <c r="J11" s="17" t="s">
         <v>85</v>
-      </c>
-      <c r="I11" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="J11" s="21" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="110.25" x14ac:dyDescent="0.25">
@@ -1463,31 +1475,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="C12" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="F12" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="D12" s="20" t="s">
-        <v>153</v>
-      </c>
-      <c r="E12" s="21" t="s">
+      <c r="G12" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="F12" s="21" t="s">
+      <c r="H12" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="G12" s="21" t="s">
+      <c r="I12" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="H12" s="21" t="s">
+      <c r="J12" s="17" t="s">
         <v>92</v>
-      </c>
-      <c r="I12" s="21" t="s">
-        <v>93</v>
-      </c>
-      <c r="J12" s="21" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="110.25" x14ac:dyDescent="0.25">
@@ -1495,31 +1507,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="C13" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="F13" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="D13" s="20" t="s">
-        <v>153</v>
-      </c>
-      <c r="E13" s="21" t="s">
+      <c r="G13" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="F13" s="21" t="s">
+      <c r="H13" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="G13" s="21" t="s">
+      <c r="I13" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="H13" s="21" t="s">
+      <c r="J13" s="17" t="s">
         <v>99</v>
-      </c>
-      <c r="I13" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="J13" s="21" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="94.5" x14ac:dyDescent="0.25">
@@ -1527,31 +1539,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="C14" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="G14" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="H14" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="D14" s="20" t="s">
-        <v>153</v>
-      </c>
-      <c r="E14" s="21" t="s">
+      <c r="I14" s="17" t="s">
         <v>175</v>
       </c>
-      <c r="F14" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="G14" s="21" t="s">
+      <c r="J14" s="17" t="s">
         <v>103</v>
-      </c>
-      <c r="H14" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="I14" s="21" t="s">
-        <v>177</v>
-      </c>
-      <c r="J14" s="21" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="110.25" x14ac:dyDescent="0.25">
@@ -1559,31 +1571,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="C15" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="F15" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="D15" s="20" t="s">
-        <v>153</v>
-      </c>
-      <c r="E15" s="21" t="s">
+      <c r="G15" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="F15" s="21" t="s">
+      <c r="H15" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="I15" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="G15" s="21" t="s">
+      <c r="J15" s="17" t="s">
         <v>109</v>
-      </c>
-      <c r="H15" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="I15" s="21" t="s">
-        <v>110</v>
-      </c>
-      <c r="J15" s="21" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="110.25" x14ac:dyDescent="0.25">
@@ -1591,63 +1603,63 @@
         <v>15</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="C16" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="F16" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="G16" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="D16" s="20" t="s">
-        <v>153</v>
-      </c>
-      <c r="E16" s="21" t="s">
+      <c r="H16" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="F16" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="G16" s="21" t="s">
+      <c r="I16" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="H16" s="21" t="s">
+      <c r="J16" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="I16" s="21" t="s">
+    </row>
+    <row r="17" spans="1:10" ht="111.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="11">
+        <v>16</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="C17" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="J16" s="21" t="s">
+      <c r="D17" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="E17" s="20" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" ht="111.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="15">
-        <v>16</v>
-      </c>
-      <c r="B17" s="16" t="s">
-        <v>167</v>
-      </c>
-      <c r="C17" s="22" t="s">
+      <c r="F17" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="D17" s="23" t="s">
-        <v>152</v>
-      </c>
-      <c r="E17" s="24" t="s">
+      <c r="G17" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="F17" s="24" t="s">
+      <c r="H17" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="G17" s="24" t="s">
+      <c r="I17" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="H17" s="24" t="s">
+      <c r="J17" s="20" t="s">
         <v>122</v>
-      </c>
-      <c r="I17" s="24" t="s">
-        <v>123</v>
-      </c>
-      <c r="J17" s="24" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="126" customHeight="1" x14ac:dyDescent="0.25">
@@ -1655,31 +1667,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="C18" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>124</v>
+      </c>
+      <c r="F18" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="D18" s="20" t="s">
-        <v>153</v>
-      </c>
-      <c r="E18" s="21" t="s">
+      <c r="G18" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="F18" s="21" t="s">
+      <c r="H18" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="G18" s="21" t="s">
+      <c r="I18" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="H18" s="21" t="s">
+      <c r="J18" s="17" t="s">
         <v>129</v>
-      </c>
-      <c r="I18" s="21" t="s">
-        <v>130</v>
-      </c>
-      <c r="J18" s="21" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="126" x14ac:dyDescent="0.25">
@@ -1687,31 +1699,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="C19" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="F19" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="D19" s="20" t="s">
-        <v>153</v>
-      </c>
-      <c r="E19" s="21" t="s">
+      <c r="G19" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="F19" s="21" t="s">
+      <c r="H19" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="G19" s="21" t="s">
+      <c r="I19" s="17" t="s">
         <v>135</v>
       </c>
-      <c r="H19" s="21" t="s">
+      <c r="J19" s="17" t="s">
         <v>136</v>
-      </c>
-      <c r="I19" s="21" t="s">
-        <v>137</v>
-      </c>
-      <c r="J19" s="21" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="110.25" x14ac:dyDescent="0.25">
@@ -1719,31 +1731,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="C20" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="F20" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="D20" s="20" t="s">
-        <v>153</v>
-      </c>
-      <c r="E20" s="21" t="s">
+      <c r="G20" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="F20" s="21" t="s">
+      <c r="H20" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="G20" s="21" t="s">
+      <c r="I20" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="H20" s="21" t="s">
+      <c r="J20" s="17" t="s">
         <v>143</v>
-      </c>
-      <c r="I20" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="J20" s="21" t="s">
-        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -1765,39 +1777,39 @@
   <sheetData>
     <row r="1" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="75" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E2" s="2">
         <v>29</v>
@@ -1811,16 +1823,16 @@
     </row>
     <row r="3" spans="1:7" ht="135" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="E3" s="2">
         <v>7</v>
@@ -1834,16 +1846,16 @@
     </row>
     <row r="4" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>149</v>
-      </c>
       <c r="D4" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
